--- a/sources/roger_step5b.xlsx
+++ b/sources/roger_step5b.xlsx
@@ -930,6 +930,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>db0103c6-cf73-4aa7-a401-ed64ab6e9ada</t>
@@ -977,6 +982,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>7e3f4889-cf90-455b-95d7-3806d4162f5d</t>
@@ -1022,6 +1032,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>217906c3-5a77-4875-a8eb-dda3b710c248</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
